--- a/data/trans_orig/P35-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P35-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007 (tasa de respuesta: 95,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>269402</t>
+          <t>274295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>329809</t>
+          <t>330431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>378925</t>
+          <t>381689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444381</t>
+          <t>451611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>671439</t>
+          <t>670305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>756145</t>
+          <t>758827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>650864</t>
+          <t>650242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>711271</t>
+          <t>706378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>810144</t>
+          <t>802914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>875600</t>
+          <t>872836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1479053</t>
+          <t>1476371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1563759</t>
+          <t>1564893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155739</t>
+          <t>152594</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>205725</t>
+          <t>203328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194773</t>
+          <t>193512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>251222</t>
+          <t>249139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360054</t>
+          <t>365138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>434596</t>
+          <t>439053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1408849</t>
+          <t>1411246</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1458835</t>
+          <t>1461980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1249973</t>
+          <t>1252056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1306422</t>
+          <t>1307683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2681173</t>
+          <t>2676716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2755715</t>
+          <t>2750631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53715</t>
+          <t>53202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87369</t>
+          <t>85294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44633</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73486</t>
+          <t>72282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105724</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149935</t>
+          <t>148899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444607</t>
+          <t>446682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478261</t>
+          <t>478774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378826</t>
+          <t>380030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>407679</t>
+          <t>408632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834353</t>
+          <t>835389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878564</t>
+          <t>877646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>504055</t>
+          <t>510422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>589433</t>
+          <t>590682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>643049</t>
+          <t>645355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>737446</t>
+          <t>734471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1182969</t>
+          <t>1178787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1304283</t>
+          <t>1297968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2537790</t>
+          <t>2536541</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2623168</t>
+          <t>2616801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2470587</t>
+          <t>2473562</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2564984</t>
+          <t>2562678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5030973</t>
+          <t>5037288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5152287</t>
+          <t>5156469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012 (tasa de respuesta: 97,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>341876</t>
+          <t>342601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>407563</t>
+          <t>402540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>548929</t>
+          <t>550612</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>625838</t>
+          <t>627715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>910242</t>
+          <t>911583</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1008478</t>
+          <t>1005000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>547805</t>
+          <t>552828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>613492</t>
+          <t>612767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>675019</t>
+          <t>673142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>751928</t>
+          <t>750245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1247747</t>
+          <t>1251225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1345983</t>
+          <t>1344642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368569</t>
+          <t>366811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>441516</t>
+          <t>444109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>437857</t>
+          <t>439464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>515985</t>
+          <t>514074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>822148</t>
+          <t>828487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>931649</t>
+          <t>932244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1454400</t>
+          <t>1451807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1527347</t>
+          <t>1529105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1186732</t>
+          <t>1188643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1264860</t>
+          <t>1263253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2666984</t>
+          <t>2666389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2776485</t>
+          <t>2770146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70683</t>
+          <t>71558</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108143</t>
+          <t>108611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103830</t>
+          <t>103194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143809</t>
+          <t>146021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186268</t>
+          <t>186293</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>238142</t>
+          <t>240238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>361110</t>
+          <t>360642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>398570</t>
+          <t>397695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300653</t>
+          <t>298441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340632</t>
+          <t>341268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675573</t>
+          <t>673477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>727447</t>
+          <t>727422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>809778</t>
+          <t>807657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>915975</t>
+          <t>916579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1125842</t>
+          <t>1129221</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1238727</t>
+          <t>1246086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1971237</t>
+          <t>1973336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2132952</t>
+          <t>2132675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2404562</t>
+          <t>2403958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2510759</t>
+          <t>2512880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2209309</t>
+          <t>2201950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2322194</t>
+          <t>2318815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4635620</t>
+          <t>4635897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4797335</t>
+          <t>4795236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016 (tasa de respuesta: 98,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285713</t>
+          <t>283116</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>338147</t>
+          <t>334799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>454240</t>
+          <t>454356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>517647</t>
+          <t>519396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>756519</t>
+          <t>756232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>840041</t>
+          <t>842833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401442</t>
+          <t>404790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453876</t>
+          <t>456473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465379</t>
+          <t>463630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>528786</t>
+          <t>528670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882574</t>
+          <t>879782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>966096</t>
+          <t>966383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>455530</t>
+          <t>451587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>529857</t>
+          <t>531541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>539916</t>
+          <t>540046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>619459</t>
+          <t>620586</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1017530</t>
+          <t>1014070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1133702</t>
+          <t>1129644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1517853</t>
+          <t>1516169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1592180</t>
+          <t>1596123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1346912</t>
+          <t>1345785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1426455</t>
+          <t>1426325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2880380</t>
+          <t>2884438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2996552</t>
+          <t>3000012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107539</t>
+          <t>107718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148681</t>
+          <t>147704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128206</t>
+          <t>128400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170157</t>
+          <t>171727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>248017</t>
+          <t>247267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307651</t>
+          <t>307420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386808</t>
+          <t>387785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427950</t>
+          <t>427771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>365966</t>
+          <t>364396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>407917</t>
+          <t>407723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>763961</t>
+          <t>764192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823595</t>
+          <t>824345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>873269</t>
+          <t>884028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>985004</t>
+          <t>981573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1160099</t>
+          <t>1155594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1278195</t>
+          <t>1271794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2054854</t>
+          <t>2071841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2224443</t>
+          <t>2223407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2337784</t>
+          <t>2341215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2449519</t>
+          <t>2438760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2207326</t>
+          <t>2213727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2325422</t>
+          <t>2329927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4583866</t>
+          <t>4584902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4753455</t>
+          <t>4736468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200559</t>
+          <t>199445</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>240256</t>
+          <t>239365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>346516</t>
+          <t>348348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>389960</t>
+          <t>389356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>557773</t>
+          <t>558262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>615692</t>
+          <t>616681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274682</t>
+          <t>275573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>314379</t>
+          <t>315493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>362262</t>
+          <t>362866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405706</t>
+          <t>403874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>651468</t>
+          <t>650479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>709387</t>
+          <t>708898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>468696</t>
+          <t>457230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>763917</t>
+          <t>761268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>491046</t>
+          <t>520033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>814688</t>
+          <t>809253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1086852</t>
+          <t>1095693</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1535456</t>
+          <t>1531956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1526410</t>
+          <t>1529059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1821631</t>
+          <t>1833097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1421226</t>
+          <t>1426661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1744868</t>
+          <t>1715881</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2990785</t>
+          <t>2994285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3439389</t>
+          <t>3430548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181704</t>
+          <t>183224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230851</t>
+          <t>233307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162653</t>
+          <t>163961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203244</t>
+          <t>203549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356717</t>
+          <t>356537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420449</t>
+          <t>421003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415772</t>
+          <t>413316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464919</t>
+          <t>463399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456759</t>
+          <t>456454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497350</t>
+          <t>496042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>886178</t>
+          <t>885624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>949910</t>
+          <t>950090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>869759</t>
+          <t>807426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1200154</t>
+          <t>1187733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1009101</t>
+          <t>1026819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1365611</t>
+          <t>1364688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2035421</t>
+          <t>1985986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2533292</t>
+          <t>2507032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2251735</t>
+          <t>2264156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2582130</t>
+          <t>2644463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2282528</t>
+          <t>2283451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2639038</t>
+          <t>2621320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4566736</t>
+          <t>4592996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5064607</t>
+          <t>5114042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P35-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>274295</t>
+          <t>272725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>330431</t>
+          <t>327560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381689</t>
+          <t>381519</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>451611</t>
+          <t>445083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>670305</t>
+          <t>669684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>758827</t>
+          <t>759069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>650242</t>
+          <t>653113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>706378</t>
+          <t>707948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>802914</t>
+          <t>809442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>872836</t>
+          <t>873006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1476371</t>
+          <t>1476129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1564893</t>
+          <t>1565514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>154453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>203328</t>
+          <t>205775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193512</t>
+          <t>194711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249139</t>
+          <t>248863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>365138</t>
+          <t>361878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>439053</t>
+          <t>439564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1411246</t>
+          <t>1408799</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1461980</t>
+          <t>1460121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1252056</t>
+          <t>1252332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1307683</t>
+          <t>1306484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2676716</t>
+          <t>2676205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2750631</t>
+          <t>2753891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53202</t>
+          <t>54776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85294</t>
+          <t>85125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>44827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>106229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148899</t>
+          <t>151014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446682</t>
+          <t>446851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478774</t>
+          <t>477200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>408632</t>
+          <t>407485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835389</t>
+          <t>833274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877646</t>
+          <t>878059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>510422</t>
+          <t>508961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>590682</t>
+          <t>587680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>645355</t>
+          <t>647402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>734471</t>
+          <t>744599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1178787</t>
+          <t>1179306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1297968</t>
+          <t>1298809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2536541</t>
+          <t>2539543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2616801</t>
+          <t>2618262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2473562</t>
+          <t>2463434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2562678</t>
+          <t>2560631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5037288</t>
+          <t>5036447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5156469</t>
+          <t>5155950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>342601</t>
+          <t>341895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>402540</t>
+          <t>403234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>550612</t>
+          <t>544749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>627715</t>
+          <t>621047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>911583</t>
+          <t>908989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1005000</t>
+          <t>1006934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>552828</t>
+          <t>552134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>612767</t>
+          <t>613473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>673142</t>
+          <t>679810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>750245</t>
+          <t>756108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1251225</t>
+          <t>1249291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1344642</t>
+          <t>1347236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>366811</t>
+          <t>367580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>444109</t>
+          <t>440514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439464</t>
+          <t>441627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>514074</t>
+          <t>514963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>828487</t>
+          <t>828601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>932244</t>
+          <t>932761</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1451807</t>
+          <t>1455402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1529105</t>
+          <t>1528336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1188643</t>
+          <t>1187754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1263253</t>
+          <t>1261090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2666389</t>
+          <t>2665872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2770146</t>
+          <t>2770032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71558</t>
+          <t>70644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108611</t>
+          <t>108168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103194</t>
+          <t>106098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146021</t>
+          <t>144709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186293</t>
+          <t>184855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240238</t>
+          <t>238639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>360642</t>
+          <t>361085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>397695</t>
+          <t>398609</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298441</t>
+          <t>299753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341268</t>
+          <t>338364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>673477</t>
+          <t>675076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>727422</t>
+          <t>728860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>807657</t>
+          <t>807358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>916579</t>
+          <t>915639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1129221</t>
+          <t>1131012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1246086</t>
+          <t>1242262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1973336</t>
+          <t>1969199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2132675</t>
+          <t>2130325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2403958</t>
+          <t>2404898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2512880</t>
+          <t>2513179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2201950</t>
+          <t>2205774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2318815</t>
+          <t>2317024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4635897</t>
+          <t>4638247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4795236</t>
+          <t>4799373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>283116</t>
+          <t>284508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>334799</t>
+          <t>338424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>454356</t>
+          <t>453139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>519396</t>
+          <t>520816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>756232</t>
+          <t>754845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>842833</t>
+          <t>839533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404790</t>
+          <t>401165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>456473</t>
+          <t>455081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>463630</t>
+          <t>462210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>528670</t>
+          <t>529887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879782</t>
+          <t>883082</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>966383</t>
+          <t>967770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>451587</t>
+          <t>454338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>531541</t>
+          <t>533849</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>540046</t>
+          <t>541317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>620586</t>
+          <t>622923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1014070</t>
+          <t>1014420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1129644</t>
+          <t>1125703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1516169</t>
+          <t>1513861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1596123</t>
+          <t>1593372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1345785</t>
+          <t>1343448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1426325</t>
+          <t>1425054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2884438</t>
+          <t>2888379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3000012</t>
+          <t>2999662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107718</t>
+          <t>107175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147704</t>
+          <t>148976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128400</t>
+          <t>129772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171727</t>
+          <t>172072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247267</t>
+          <t>248233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307420</t>
+          <t>306154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387785</t>
+          <t>386513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427771</t>
+          <t>428314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>364396</t>
+          <t>364051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>407723</t>
+          <t>406351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764192</t>
+          <t>765458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824345</t>
+          <t>823379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>884028</t>
+          <t>877168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>981573</t>
+          <t>985925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1155594</t>
+          <t>1162432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1271794</t>
+          <t>1277355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2071841</t>
+          <t>2063326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2223407</t>
+          <t>2223349</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2341215</t>
+          <t>2336863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2438760</t>
+          <t>2445620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2213727</t>
+          <t>2208166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2329927</t>
+          <t>2323089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4584902</t>
+          <t>4584960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4736468</t>
+          <t>4744983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>218432</t>
+          <t>237854</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199445</t>
+          <t>214507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239365</t>
+          <t>261348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>368488</t>
+          <t>399021</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>348348</t>
+          <t>377450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>389356</t>
+          <t>421224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>586920</t>
+          <t>636876</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558262</t>
+          <t>603328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>616681</t>
+          <t>667569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>296506</t>
+          <t>340675</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275573</t>
+          <t>317181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315493</t>
+          <t>364022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>383734</t>
+          <t>421272</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>362866</t>
+          <t>399069</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>403874</t>
+          <t>442843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>680240</t>
+          <t>761947</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>650479</t>
+          <t>731254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708898</t>
+          <t>795495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752222</t>
+          <t>820293</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752222</t>
+          <t>820293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752222</t>
+          <t>820293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267160</t>
+          <t>1398823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267160</t>
+          <t>1398823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267160</t>
+          <t>1398823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>665122</t>
+          <t>743060</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>457230</t>
+          <t>696483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>761268</t>
+          <t>792526</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>709944</t>
+          <t>804108</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>520033</t>
+          <t>760373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>809253</t>
+          <t>845579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1375066</t>
+          <t>1547168</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1095693</t>
+          <t>1474968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1531956</t>
+          <t>1609196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1625205</t>
+          <t>1487506</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1529059</t>
+          <t>1438040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1833097</t>
+          <t>1534083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1525970</t>
+          <t>1365336</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1426661</t>
+          <t>1323865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1715881</t>
+          <t>1409071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3151175</t>
+          <t>2852843</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2994285</t>
+          <t>2790815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3430548</t>
+          <t>2925043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235914</t>
+          <t>2169444</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235914</t>
+          <t>2169444</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235914</t>
+          <t>2169444</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526241</t>
+          <t>4400011</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526241</t>
+          <t>4400011</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526241</t>
+          <t>4400011</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>206304</t>
+          <t>231695</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>183224</t>
+          <t>207192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>233307</t>
+          <t>259240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>182087</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163961</t>
+          <t>185576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203549</t>
+          <t>229867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>388392</t>
+          <t>438433</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356537</t>
+          <t>407055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421003</t>
+          <t>475761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>440319</t>
+          <t>479892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413316</t>
+          <t>452347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463399</t>
+          <t>504395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>477916</t>
+          <t>527655</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456454</t>
+          <t>504526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>496042</t>
+          <t>548817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>918235</t>
+          <t>1007547</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>885624</t>
+          <t>970219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>950090</t>
+          <t>1038925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660003</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660003</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660003</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306627</t>
+          <t>1445980</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306627</t>
+          <t>1445980</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306627</t>
+          <t>1445980</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1089858</t>
+          <t>1212610</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>807426</t>
+          <t>1151181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1187733</t>
+          <t>1277155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1260519</t>
+          <t>1409867</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1026819</t>
+          <t>1360566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1364688</t>
+          <t>1462509</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2350378</t>
+          <t>2622476</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1985986</t>
+          <t>2544011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2507032</t>
+          <t>2699647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2362031</t>
+          <t>2308073</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2264156</t>
+          <t>2243528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2644463</t>
+          <t>2369502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2387620</t>
+          <t>2314263</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2283451</t>
+          <t>2261621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2621320</t>
+          <t>2363564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4749650</t>
+          <t>4622337</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4592996</t>
+          <t>4545166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5114042</t>
+          <t>4700802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648139</t>
+          <t>3724130</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648139</t>
+          <t>3724130</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648139</t>
+          <t>3724130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7100028</t>
+          <t>7244813</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7100028</t>
+          <t>7244813</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7100028</t>
+          <t>7244813</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
